--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-methacholine.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-methacholine.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7866" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7866" uniqueCount="592">
   <si>
     <t>Property</t>
   </si>
@@ -1117,89 +1117,93 @@
     <t>The ingredients need not be a complete list.  If an ingredient is not specified, this does not indicate whether an ingredient is present or absent.  If an ingredient is specified it does not mean that all ingredients are specified.  It is possible to specify both inactive and active ingredients.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:isActive}
+</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension:Wirkstofftyp</t>
+  </si>
+  <si>
+    <t>Wirkstofftyp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-medikation/StructureDefinition/wirkstofftyp}
+</t>
+  </si>
+  <si>
+    <t>MII EX Medikation Wirkstofftyp</t>
+  </si>
+  <si>
+    <t>Extension zur Differenzierung des Wirkstofftyps in allgemeinen, genauen oder Kombinationswirkstoff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension:Wirkstoffrelation</t>
+  </si>
+  <si>
+    <t>Wirkstoffrelation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-medikation/StructureDefinition/wirkstoffrelation}
+</t>
+  </si>
+  <si>
+    <t>MII EX Medikation Wirkstoffrelation</t>
+  </si>
+  <si>
+    <t>Die Extension ermöglicht die Zuordnung von einem genauem Wirkstoff (z.B. Salz, Ester) zu einem allgemeinem Wirkstoff.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
+  </si>
+  <si>
+    <t>The actual ingredient or content</t>
+  </si>
+  <si>
+    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
+  </si>
+  <si>
+    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
+  </si>
+  <si>
     <t xml:space="preserve">type:$this}
 </t>
-  </si>
-  <si>
-    <t>Medication.ingredient.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension:Wirkstofftyp</t>
-  </si>
-  <si>
-    <t>Wirkstofftyp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-medikation/StructureDefinition/wirkstofftyp}
-</t>
-  </si>
-  <si>
-    <t>MII EX Medikation Wirkstofftyp</t>
-  </si>
-  <si>
-    <t>Extension zur Differenzierung des Wirkstofftyps in allgemeinen, genauen oder Kombinationswirkstoff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension:Wirkstoffrelation</t>
-  </si>
-  <si>
-    <t>Wirkstoffrelation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-medikation/StructureDefinition/wirkstoffrelation}
-</t>
-  </si>
-  <si>
-    <t>MII EX Medikation Wirkstoffrelation</t>
-  </si>
-  <si>
-    <t>Die Extension ermöglicht die Zuordnung von einem genauem Wirkstoff (z.B. Salz, Ester) zu einem allgemeinem Wirkstoff.</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
-  </si>
-  <si>
-    <t>The actual ingredient or content</t>
-  </si>
-  <si>
-    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
-  </si>
-  <si>
-    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
     <t>closed</t>
@@ -10100,14 +10104,14 @@
         <v>76</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="AC71" s="2"/>
       <c r="AD71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>370</v>
@@ -10131,18 +10135,18 @@
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>76</v>
@@ -10164,7 +10168,7 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>372</v>
@@ -10244,18 +10248,18 @@
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>76</v>
@@ -10357,15 +10361,15 @@
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10471,10 +10475,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10582,10 +10586,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10693,13 +10697,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>76</v>
@@ -10724,10 +10728,10 @@
         <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>211</v>
@@ -10743,7 +10747,7 @@
         <v>76</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>76</v>
@@ -10762,7 +10766,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>76</v>
@@ -10806,10 +10810,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10915,10 +10919,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11026,10 +11030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11139,10 +11143,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11250,10 +11254,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11361,10 +11365,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11472,10 +11476,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11585,13 +11589,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>76</v>
@@ -11616,10 +11620,10 @@
         <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>211</v>
@@ -11635,7 +11639,7 @@
         <v>76</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>76</v>
@@ -11654,7 +11658,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11698,10 +11702,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11807,10 +11811,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11918,10 +11922,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12031,10 +12035,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12142,10 +12146,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12253,10 +12257,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12364,10 +12368,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12477,13 +12481,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>76</v>
@@ -12508,10 +12512,10 @@
         <v>139</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>211</v>
@@ -12527,7 +12531,7 @@
         <v>76</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>76</v>
@@ -12592,10 +12596,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12701,10 +12705,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12812,10 +12816,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12925,10 +12929,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13036,10 +13040,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13147,10 +13151,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13258,10 +13262,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13371,13 +13375,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>76</v>
@@ -13402,10 +13406,10 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>211</v>
@@ -13421,7 +13425,7 @@
         <v>76</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>76</v>
@@ -13486,10 +13490,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13595,10 +13599,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13706,10 +13710,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13819,10 +13823,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13930,10 +13934,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14041,10 +14045,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14152,10 +14156,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14265,10 +14269,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14378,10 +14382,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14407,14 +14411,14 @@
         <v>256</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>76</v>
@@ -14463,7 +14467,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14489,10 +14493,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14518,10 +14522,10 @@
         <v>341</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14572,7 +14576,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14587,21 +14591,21 @@
         <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14707,10 +14711,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14818,10 +14822,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14844,13 +14848,13 @@
         <v>87</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14901,7 +14905,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14927,10 +14931,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14953,13 +14957,13 @@
         <v>87</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15010,7 +15014,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15036,13 +15040,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>344</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>76</v>
@@ -15149,7 +15153,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>350</v>
@@ -15258,7 +15262,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>351</v>
@@ -15365,7 +15369,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>351</v>
@@ -15476,7 +15480,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>351</v>
@@ -15587,7 +15591,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>365</v>
@@ -15700,7 +15704,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>370</v>
@@ -15773,14 +15777,14 @@
         <v>76</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>370</v>
@@ -15804,18 +15808,18 @@
         <v>76</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>76</v>
@@ -15917,15 +15921,15 @@
         <v>76</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16031,10 +16035,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16142,10 +16146,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16253,13 +16257,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>76</v>
@@ -16284,10 +16288,10 @@
         <v>139</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>211</v>
@@ -16303,7 +16307,7 @@
         <v>76</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>76</v>
@@ -16322,7 +16326,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>76</v>
@@ -16366,10 +16370,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16475,10 +16479,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16586,10 +16590,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16699,10 +16703,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16810,10 +16814,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16921,10 +16925,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17032,10 +17036,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17145,13 +17149,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>76</v>
@@ -17176,10 +17180,10 @@
         <v>139</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>211</v>
@@ -17195,7 +17199,7 @@
         <v>76</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>76</v>
@@ -17214,7 +17218,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -17258,10 +17262,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17367,10 +17371,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17478,10 +17482,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17591,10 +17595,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17702,10 +17706,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17813,10 +17817,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17924,10 +17928,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18037,13 +18041,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>76</v>
@@ -18068,10 +18072,10 @@
         <v>139</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>211</v>
@@ -18087,7 +18091,7 @@
         <v>76</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>76</v>
@@ -18152,10 +18156,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18261,10 +18265,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18372,10 +18376,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18485,10 +18489,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18596,10 +18600,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18707,10 +18711,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18818,10 +18822,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18931,13 +18935,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>76</v>
@@ -18962,10 +18966,10 @@
         <v>139</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>211</v>
@@ -18981,7 +18985,7 @@
         <v>76</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>76</v>
@@ -19046,10 +19050,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19155,10 +19159,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19266,10 +19270,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19379,10 +19383,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19490,10 +19494,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19601,10 +19605,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19712,10 +19716,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19825,10 +19829,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19938,13 +19942,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>76</v>
@@ -19966,7 +19970,7 @@
         <v>76</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>372</v>
@@ -20046,15 +20050,15 @@
         <v>76</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20062,7 +20066,7 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>86</v>
@@ -20080,14 +20084,14 @@
         <v>256</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>76</v>
@@ -20097,7 +20101,7 @@
         <v>76</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>76</v>
@@ -20136,7 +20140,7 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
@@ -20162,10 +20166,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20191,10 +20195,10 @@
         <v>341</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20245,7 +20249,7 @@
         <v>76</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>77</v>
@@ -20260,21 +20264,21 @@
         <v>98</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20380,10 +20384,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20491,10 +20495,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20517,13 +20521,13 @@
         <v>87</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20535,7 +20539,7 @@
         <v>76</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T165" t="s" s="2">
         <v>76</v>
@@ -20574,7 +20578,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -20600,10 +20604,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20626,13 +20630,13 @@
         <v>87</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20644,7 +20648,7 @@
         <v>76</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>76</v>
@@ -20683,7 +20687,7 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -20709,13 +20713,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>344</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>76</v>
@@ -20822,7 +20826,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>350</v>
@@ -20931,7 +20935,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>351</v>
@@ -21038,7 +21042,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>351</v>
@@ -21149,7 +21153,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>351</v>
@@ -21260,7 +21264,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>365</v>
@@ -21373,7 +21377,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>370</v>
@@ -21446,14 +21450,14 @@
         <v>76</v>
       </c>
       <c r="AB173" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="AC173" s="2"/>
       <c r="AD173" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF173" t="s" s="2">
         <v>370</v>
@@ -21477,18 +21481,18 @@
         <v>76</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>76</v>
@@ -21590,15 +21594,15 @@
         <v>76</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21704,10 +21708,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21815,10 +21819,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21926,13 +21930,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>76</v>
@@ -21957,10 +21961,10 @@
         <v>139</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>211</v>
@@ -21976,7 +21980,7 @@
         <v>76</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>76</v>
@@ -21995,7 +21999,7 @@
       </c>
       <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>76</v>
@@ -22039,10 +22043,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22148,10 +22152,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22259,10 +22263,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22372,10 +22376,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22483,10 +22487,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22594,10 +22598,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22705,10 +22709,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -22818,13 +22822,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>76</v>
@@ -22849,10 +22853,10 @@
         <v>139</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N186" t="s" s="2">
         <v>211</v>
@@ -22868,7 +22872,7 @@
         <v>76</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>76</v>
@@ -22887,7 +22891,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>76</v>
@@ -22931,10 +22935,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23040,10 +23044,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23151,10 +23155,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23264,10 +23268,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23375,10 +23379,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23486,10 +23490,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23597,10 +23601,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23710,13 +23714,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>76</v>
@@ -23741,10 +23745,10 @@
         <v>139</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N194" t="s" s="2">
         <v>211</v>
@@ -23760,7 +23764,7 @@
         <v>76</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>76</v>
@@ -23825,10 +23829,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -23934,10 +23938,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24045,10 +24049,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24158,10 +24162,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24269,10 +24273,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24380,10 +24384,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24491,10 +24495,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24604,13 +24608,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>76</v>
@@ -24635,10 +24639,10 @@
         <v>139</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N202" t="s" s="2">
         <v>211</v>
@@ -24654,7 +24658,7 @@
         <v>76</v>
       </c>
       <c r="S202" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="T202" t="s" s="2">
         <v>76</v>
@@ -24719,10 +24723,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24828,10 +24832,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -24939,10 +24943,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25052,10 +25056,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25163,10 +25167,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25274,10 +25278,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25385,10 +25389,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25498,10 +25502,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25611,13 +25615,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>370</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>76</v>
@@ -25639,7 +25643,7 @@
         <v>76</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L211" t="s" s="2">
         <v>372</v>
@@ -25719,15 +25723,15 @@
         <v>76</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -25735,7 +25739,7 @@
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G212" t="s" s="2">
         <v>86</v>
@@ -25753,14 +25757,14 @@
         <v>256</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>76</v>
@@ -25809,7 +25813,7 @@
         <v>76</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -25835,10 +25839,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -25864,10 +25868,10 @@
         <v>341</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -25918,7 +25922,7 @@
         <v>76</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>77</v>
@@ -25933,21 +25937,21 @@
         <v>98</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26053,10 +26057,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26164,10 +26168,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26190,13 +26194,13 @@
         <v>87</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -26247,7 +26251,7 @@
         <v>76</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>77</v>
@@ -26273,10 +26277,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26299,13 +26303,13 @@
         <v>87</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -26356,7 +26360,7 @@
         <v>76</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>77</v>
@@ -26382,10 +26386,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26411,10 +26415,10 @@
         <v>345</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -26465,7 +26469,7 @@
         <v>76</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
@@ -26491,10 +26495,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26600,10 +26604,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26711,10 +26715,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26824,10 +26828,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -26853,10 +26857,10 @@
         <v>100</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -26907,7 +26911,7 @@
         <v>76</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>77</v>
@@ -26928,15 +26932,15 @@
         <v>76</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -26959,13 +26963,13 @@
         <v>76</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -27016,7 +27020,7 @@
         <v>76</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>77</v>
@@ -27037,7 +27041,7 @@
         <v>76</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
